--- a/Luaban/MiniTemplate/Datas/#SkillEffectInfo.xlsx
+++ b/Luaban/MiniTemplate/Datas/#SkillEffectInfo.xlsx
@@ -754,6 +754,63 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="1">
+        <x:v>2008001</x:v>
+      </x:c>
+      <x:c r="C9" s="1">
+        <x:v>10080</x:v>
+      </x:c>
+      <x:c r="D9" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="1">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="G9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="1">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="J9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
